--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>79.47158346516349</v>
+        <v>12.91413231308907</v>
       </c>
       <c r="D2" t="n">
-        <v>79.44467273014364</v>
+        <v>12.90975931864834</v>
       </c>
       <c r="E2" t="n">
-        <v>16.97509362945815</v>
+        <v>2.75845271478695</v>
       </c>
       <c r="F2" t="n">
-        <v>16.91627242193225</v>
+        <v>2.748894268563991</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>63.68029202104402</v>
+        <v>10.34804745341965</v>
       </c>
       <c r="D3" t="n">
-        <v>63.57493049731169</v>
+        <v>10.33092620581315</v>
       </c>
       <c r="E3" t="n">
-        <v>16.97509362945815</v>
+        <v>2.75845271478695</v>
       </c>
       <c r="F3" t="n">
-        <v>16.91627242193225</v>
+        <v>2.748894268563991</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.82421534143267</v>
+        <v>8.58393499298281</v>
       </c>
       <c r="D4" t="n">
-        <v>52.85086767056201</v>
+        <v>8.588265996466326</v>
       </c>
       <c r="E4" t="n">
-        <v>16.97509362945815</v>
+        <v>2.75845271478695</v>
       </c>
       <c r="F4" t="n">
-        <v>16.91627242193225</v>
+        <v>2.748894268563991</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.64219774193703</v>
+        <v>5.629357133064768</v>
       </c>
       <c r="D5" t="n">
-        <v>34.79678710192327</v>
+        <v>5.654477904062531</v>
       </c>
       <c r="E5" t="n">
-        <v>16.97509362945815</v>
+        <v>2.75845271478695</v>
       </c>
       <c r="F5" t="n">
-        <v>16.91627242193225</v>
+        <v>2.748894268563991</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.4407905785726</v>
+        <v>4.784128469018047</v>
       </c>
       <c r="D6" t="n">
-        <v>29.52061859063211</v>
+        <v>4.797100520977717</v>
       </c>
       <c r="E6" t="n">
-        <v>16.97509362945815</v>
+        <v>2.75845271478695</v>
       </c>
       <c r="F6" t="n">
-        <v>16.91627242193225</v>
+        <v>2.748894268563991</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>57.69503753389353</v>
+        <v>9.3754435992577</v>
       </c>
       <c r="D7" t="n">
-        <v>57.81157079452376</v>
+        <v>9.394380254110111</v>
       </c>
       <c r="E7" t="n">
-        <v>16.97509362945815</v>
+        <v>2.75845271478695</v>
       </c>
       <c r="F7" t="n">
-        <v>16.91627242193225</v>
+        <v>2.748894268563991</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
